--- a/ASME B18.2.8-1999 CLEARANCE HOLES FOR BOLTS, SCREWS, AND STUDS.xlsx
+++ b/ASME B18.2.8-1999 CLEARANCE HOLES FOR BOLTS, SCREWS, AND STUDS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="12" windowWidth="20952" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="12" windowWidth="20952" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Metric" sheetId="1" r:id="rId1"/>
@@ -8035,6 +8035,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="10">
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="E2:F2"/>
